--- a/output/pdf_financials_xlsx/CKI.xlsx
+++ b/output/pdf_financials_xlsx/CKI.xlsx
@@ -1126,19 +1126,19 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>4.126</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>2.665</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>1.746</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.774</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.173</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>0</v>
@@ -2185,19 +2185,19 @@
         <v>38.543</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>43.003</v>
+        <v>38.877</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-8.513</v>
+        <v>-11.178</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>24.744</v>
+        <v>22.998</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>5.785</v>
+        <v>5.011</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.052</v>
+        <v>-0.225</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>32.605</v>
@@ -2315,19 +2315,19 @@
         <v>39.752</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>43.959</v>
+        <v>39.833</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-8.076000000000001</v>
+        <v>-10.741</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>24.744</v>
+        <v>22.998</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>5.785</v>
+        <v>5.011</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.052</v>
+        <v>-0.225</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>32.605</v>
@@ -2380,19 +2380,19 @@
         <v>75.0831066787549</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>78.86295545469224</v>
+        <v>71.4608636371791</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-1460.397830018083</v>
+        <v>-1942.314647377939</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>75.58651026392963</v>
+        <v>70.25293255131965</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>43.76276571601483</v>
+        <v>37.90755730388078</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-0.7516623301532235</v>
+        <v>-3.252385082393756</v>
       </c>
       <c r="L30" s="1" t="inlineStr">
         <is>
@@ -2620,13 +2620,13 @@
         <v>1.09</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.929</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -2734,13 +2734,13 @@
         <v>1.09</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.929</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -3418,13 +3418,13 @@
         <v>71.721</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>11.679</v>
+        <v>10.75</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>1.863</v>
+        <v>1.054</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>2.213</v>
+        <v>1.653</v>
       </c>
     </row>
     <row r="49">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -57096,7 +57096,7 @@
       </c>
       <c r="D512" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E512" t="inlineStr">
@@ -57650,7 +57650,7 @@
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
@@ -58694,7 +58694,7 @@
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
@@ -59936,7 +59936,7 @@
       </c>
       <c r="D542" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E542" t="inlineStr">
@@ -61288,7 +61288,7 @@
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">

--- a/output/pdf_financials_xlsx/CKI.xlsx
+++ b/output/pdf_financials_xlsx/CKI.xlsx
@@ -7118,10 +7118,10 @@
         <v>0</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="L112" s="3" t="n">
-        <v>0</v>
+        <v>66.566</v>
       </c>
       <c r="M112" s="3" t="n">
         <v>0</v>
@@ -40996,7 +40996,11 @@
           <t>Proceeds on disposition of property and equipment</t>
         </is>
       </c>
-      <c r="D342" t="inlineStr"/>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E342" t="inlineStr">
         <is>
           <t>-</t>
